--- a/Wikidata Delta/pk_gen_excels/pep_pakistan_living_relevant_rca_lookup.xlsx
+++ b/Wikidata Delta/pk_gen_excels/pep_pakistan_living_relevant_rca_lookup.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="203">
   <si>
     <r>
       <rPr>
@@ -29,6 +29,14 @@
         <b/>
       </rPr>
       <t>RCA ID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
   </si>
   <si>
@@ -792,819 +800,843 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr defaultRowHeight="12.8" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="11.53515625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="29.12" customWidth="1"/>
     <col min="2" max="2" width="26.48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" ht="12.8" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="2" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B42" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B44" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B48" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="49" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B49" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B51" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B52" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="53" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B53" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B54" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B55" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B56" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="57" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B57" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="58" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B58" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B59" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="60" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B60" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="61" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B61" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="62" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B62" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="63" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B63" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="64" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B64" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="65" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B65" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="66" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B66" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="67" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B67" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="68" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B68" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="69" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B69" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="70" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B70" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="71" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B71" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="72" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B72" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="73" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B73" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="74" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B74" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="75" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B75" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="76" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B76" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="77" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B77" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="78" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B78" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="79" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B79" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="80" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B80" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="81" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B81" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="82" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B82" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="83" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B83" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="84" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B84" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="85" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B85" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="86" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B86" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="87" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B87" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="88" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B88" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="89" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B89" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="90" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B90" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="91" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B91" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="92" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B92" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="93" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B93" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="94" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B94" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="95" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B95" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="96" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B96" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="97" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B97" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="98" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B98" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="99" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B99" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="100" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B100" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="101" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B101" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/Wikidata Delta/pk_gen_excels/pep_pakistan_living_relevant_rca_lookup.xlsx
+++ b/Wikidata Delta/pk_gen_excels/pep_pakistan_living_relevant_rca_lookup.xlsx
@@ -4,17 +4,17 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25000" windowHeight="10000" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="pakistan_rca_5-may" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Sheet0" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="355">
   <si>
     <r>
       <rPr>
@@ -639,14 +639,482 @@
   <si>
     <t>PK-GEN-RSS-9WXPP-RCA-1</t>
   </si>
+  <si>
+    <t>Bobby Hajjaj</t>
+  </si>
+  <si>
+    <t>PK-GEN-BH-SZYEX-RCA-1</t>
+  </si>
+  <si>
+    <t>Aaminah Haq</t>
+  </si>
+  <si>
+    <t>PK-GEN-AH-SJE29-RCA-1</t>
+  </si>
+  <si>
+    <t>Muhammad Hamza Shahbaz Sharif</t>
+  </si>
+  <si>
+    <t>PK-GEN-MHSS-3QY3D-RCA-1</t>
+  </si>
+  <si>
+    <t>Rabia Imran</t>
+  </si>
+  <si>
+    <t>PK-GEN-RI-34KVZ-RCA-1</t>
+  </si>
+  <si>
+    <t>Suleman Shahbaz</t>
+  </si>
+  <si>
+    <t>PK-GEN-SS-WJ6YU-RCA-1</t>
+  </si>
+  <si>
+    <t>Syed Mustafa Mahmud</t>
+  </si>
+  <si>
+    <t>PK-GEN-SMM-N7D4K-RCA-1</t>
+  </si>
+  <si>
+    <t>Chaudhry Salik Hussain</t>
+  </si>
+  <si>
+    <t>PK-GEN-CSH-JQP93-RCA-1</t>
+  </si>
+  <si>
+    <t>Hasnain Ali Mirza</t>
+  </si>
+  <si>
+    <t>PK-GEN-HAM-UWBFU-RCA-1</t>
+  </si>
+  <si>
+    <t>Moonis Elahi</t>
+  </si>
+  <si>
+    <t>PK-GEN-ME-LEC7K-RCA-1</t>
+  </si>
+  <si>
+    <t>Asjad Mahmood</t>
+  </si>
+  <si>
+    <t>PK-GEN-AM-53ZC6-RCA-1</t>
+  </si>
+  <si>
+    <t>Mamoona Hashmi</t>
+  </si>
+  <si>
+    <t>PK-GEN-MH-N189F-RCA-1</t>
+  </si>
+  <si>
+    <t>Ali Dar</t>
+  </si>
+  <si>
+    <t>PK-GEN-AD-8G5AA-RCA-1</t>
+  </si>
+  <si>
+    <t>Mr Rejwan Ahammad Taufiq</t>
+  </si>
+  <si>
+    <t>PK-GEN-MRAT-4GYAV-RCA-1</t>
+  </si>
+  <si>
+    <t>Sara Hossain</t>
+  </si>
+  <si>
+    <t>PK-GEN-SH-ZD2QC-RCA-1</t>
+  </si>
+  <si>
+    <t>Anas Sarwar</t>
+  </si>
+  <si>
+    <t>PK-GEN-AS-2K5AM-RCA-1</t>
+  </si>
+  <si>
+    <t>Nafisa Shah</t>
+  </si>
+  <si>
+    <t>PK-GEN-NS-YOXNW-RCA-1</t>
+  </si>
+  <si>
+    <t>Tania Amir</t>
+  </si>
+  <si>
+    <t>PK-GEN-TA-4382O-RCA-1</t>
+  </si>
+  <si>
+    <t>Arina Aamir Sheikh</t>
+  </si>
+  <si>
+    <t>PK-GEN-AAS-2XE9L-RCA-1</t>
+  </si>
+  <si>
+    <t>Osman Saifullah</t>
+  </si>
+  <si>
+    <t>PK-GEN-OS-JS1LP-RCA-1</t>
+  </si>
+  <si>
+    <t>Ehsan Riaz Fatyana</t>
+  </si>
+  <si>
+    <t>PK-GEN-ERF-TUEU2-RCA-1</t>
+  </si>
+  <si>
+    <t>Bakhtawar Bhutto Zardari</t>
+  </si>
+  <si>
+    <t>PK-GEN-BBZ-SWLUE-RCA-1</t>
+  </si>
+  <si>
+    <t>Bilawal Bhutto Zardari</t>
+  </si>
+  <si>
+    <t>PK-GEN-BBZ-CV1QK-RCA-1</t>
+  </si>
+  <si>
+    <t>Abdul Samad Dawood</t>
+  </si>
+  <si>
+    <t>PK-GEN-ASD-1RWWD-RCA-1</t>
+  </si>
+  <si>
+    <t>Azmeh Dawood</t>
+  </si>
+  <si>
+    <t>PK-GEN-AD-WL3EV-RCA-1</t>
+  </si>
+  <si>
+    <t>Sabrina Dawood</t>
+  </si>
+  <si>
+    <t>PK-GEN-SD-RRZYR-RCA-1</t>
+  </si>
+  <si>
+    <t>Shahzada Dawood</t>
+  </si>
+  <si>
+    <t>PK-GEN-SD-WNDML-RCA-1</t>
+  </si>
+  <si>
+    <t>Ali Sethi</t>
+  </si>
+  <si>
+    <t>PK-GEN-AS-02UYM-RCA-1</t>
+  </si>
+  <si>
+    <t>Mira Sethi</t>
+  </si>
+  <si>
+    <t>PK-GEN-MS-EZNVP-RCA-1</t>
+  </si>
+  <si>
+    <t>Khandakar Masrur Hossain Mitu</t>
+  </si>
+  <si>
+    <t>PK-GEN-KMHM-GWTS3-RCA-1</t>
+  </si>
+  <si>
+    <t>Mahnoor Safdar</t>
+  </si>
+  <si>
+    <t>PK-GEN-MS-965EI-RCA-1</t>
+  </si>
+  <si>
+    <t>Mehr un Nisa Munir</t>
+  </si>
+  <si>
+    <t>PK-GEN-MUNM-ICN1C-RCA-1</t>
+  </si>
+  <si>
+    <t>Waleed Iqbal</t>
+  </si>
+  <si>
+    <t>PK-GEN-WI-PR3F3-RCA-1</t>
+  </si>
+  <si>
+    <t>Marvi Pir Mazhar</t>
+  </si>
+  <si>
+    <t>PK-GEN-MPM-U61PU-RCA-1</t>
+  </si>
+  <si>
+    <t>Sheikh Fazle Fahim</t>
+  </si>
+  <si>
+    <t>PK-GEN-SFF-YJ8ND-RCA-1</t>
+  </si>
+  <si>
+    <t>Dia Chakravarti</t>
+  </si>
+  <si>
+    <t>PK-GEN-DC-CIPUP-RCA-1</t>
+  </si>
+  <si>
+    <t>Hafiz Anas Hussain Rizvi</t>
+  </si>
+  <si>
+    <t>PK-GEN-HAHR-6VXRD-RCA-1</t>
+  </si>
+  <si>
+    <t>Hamid Khan Achakzai</t>
+  </si>
+  <si>
+    <t>PK-GEN-HKA-4G5HO-RCA-1</t>
+  </si>
+  <si>
+    <t>Muhammad Khan Achakzai</t>
+  </si>
+  <si>
+    <t>PK-GEN-MKA-LF75M-RCA-1</t>
+  </si>
+  <si>
+    <t>Mufti Abu Lubaba</t>
+  </si>
+  <si>
+    <t>PK-GEN-MAL-BDAY5-RCA-1</t>
+  </si>
+  <si>
+    <t>Abbas Sharif</t>
+  </si>
+  <si>
+    <t>PK-GEN-AS-1T6QQ-RCA-1</t>
+  </si>
+  <si>
+    <t>Shehbaz Sharif</t>
+  </si>
+  <si>
+    <t>PK-GEN-SS-HQPTB-RCA-1</t>
+  </si>
+  <si>
+    <t>Liaquat Khan</t>
+  </si>
+  <si>
+    <t>PK-GEN-LK-HWDRG-RCA-1</t>
+  </si>
+  <si>
+    <t>Balach Marri</t>
+  </si>
+  <si>
+    <t>PK-GEN-BM-AI6E1-RCA-1</t>
+  </si>
+  <si>
+    <t>Brahumdagh Bugti</t>
+  </si>
+  <si>
+    <t>PK-GEN-BB-63CDQ-RCA-1</t>
+  </si>
+  <si>
+    <t>Changez Marri</t>
+  </si>
+  <si>
+    <t>PK-GEN-CM-DQK01-RCA-1</t>
+  </si>
+  <si>
+    <t>Ghazan Marri</t>
+  </si>
+  <si>
+    <t>PK-GEN-GM-VPVJ6-RCA-1</t>
+  </si>
+  <si>
+    <t>Hyrbyair Marri</t>
+  </si>
+  <si>
+    <t>PK-GEN-HM-RRP73-RCA-1</t>
+  </si>
+  <si>
+    <t>Mehran Marri</t>
+  </si>
+  <si>
+    <t>PK-GEN-MM-69W1U-RCA-1</t>
+  </si>
+  <si>
+    <t>Tahir Bashir Cheema</t>
+  </si>
+  <si>
+    <t>PK-GEN-TBC-2C9NY-RCA-1</t>
+  </si>
+  <si>
+    <t>Ghulam Noor Rabbani Khar</t>
+  </si>
+  <si>
+    <t>PK-GEN-GNRK-VXXE5-RCA-1</t>
+  </si>
+  <si>
+    <t>Aseefa Bhutto Zardari</t>
+  </si>
+  <si>
+    <t>PK-GEN-ABZ-1P3LB-RCA-1</t>
+  </si>
+  <si>
+    <t>Nawaz Sharif</t>
+  </si>
+  <si>
+    <t>PK-GEN-NS-5DWON-RCA-1</t>
+  </si>
+  <si>
+    <t>Kazi Asad Abid</t>
+  </si>
+  <si>
+    <t>PK-GEN-KAA-76F94-RCA-1</t>
+  </si>
+  <si>
+    <t>Raza Rabbani Khar</t>
+  </si>
+  <si>
+    <t>PK-GEN-RRK-ZJKQI-RCA-1</t>
+  </si>
+  <si>
+    <t>Atta ur Rehman</t>
+  </si>
+  <si>
+    <t>PK-GEN-AUR-YJ7B8-RCA-1</t>
+  </si>
+  <si>
+    <t>Latuf Ur Rehman</t>
+  </si>
+  <si>
+    <t>PK-GEN-LUR-9G7ZO-RCA-1</t>
+  </si>
+  <si>
+    <t>Zia ur Rehman</t>
+  </si>
+  <si>
+    <t>PK-GEN-ZUR-H7ZYH-RCA-1</t>
+  </si>
+  <si>
+    <t>Asif Ali Zardari</t>
+  </si>
+  <si>
+    <t>PK-GEN-AAZ-4U3F4-RCA-1</t>
+  </si>
+  <si>
+    <t>Javed Fiyaz</t>
+  </si>
+  <si>
+    <t>PK-GEN-JF-VTK0F-RCA-1</t>
+  </si>
+  <si>
+    <t>Muhammad Saleem Baryar</t>
+  </si>
+  <si>
+    <t>PK-GEN-MSB-TN8KR-RCA-1</t>
+  </si>
+  <si>
+    <t>Tariq Bajwa</t>
+  </si>
+  <si>
+    <t>PK-GEN-TB-MX39R-RCA-1</t>
+  </si>
+  <si>
+    <t>Faryal Talpur</t>
+  </si>
+  <si>
+    <t>PK-GEN-FT-YVD4P-RCA-1</t>
+  </si>
+  <si>
+    <t>Azra Fazal Pechuho</t>
+  </si>
+  <si>
+    <t>PK-GEN-AFP-T741C-RCA-1</t>
+  </si>
+  <si>
+    <t>Hameed Haroon</t>
+  </si>
+  <si>
+    <t>PK-GEN-HH-6EHE5-RCA-1</t>
+  </si>
+  <si>
+    <t>Alamgir Tareen</t>
+  </si>
+  <si>
+    <t>PK-GEN-AT-NE58S-RCA-1</t>
+  </si>
+  <si>
+    <t>Moni Mohsin</t>
+  </si>
+  <si>
+    <t>PK-GEN-MM-XUV60-RCA-1</t>
+  </si>
+  <si>
+    <t>Fatima Bhutto</t>
+  </si>
+  <si>
+    <t>PK-GEN-FB-CU197-RCA-1</t>
+  </si>
+  <si>
+    <t>Hussain Haroon</t>
+  </si>
+  <si>
+    <t>PK-GEN-HH-FP3PV-RCA-1</t>
+  </si>
+  <si>
+    <t>Nasir Mahmood Khosa</t>
+  </si>
+  <si>
+    <t>PK-GEN-NMK-FFZ7J-RCA-1</t>
+  </si>
+  <si>
+    <t>Fazal ur Rehman</t>
+  </si>
+  <si>
+    <t>PK-GEN-FUR-C5DCT-RCA-1</t>
+  </si>
+  <si>
+    <t>A Z M Enayetullah Khan</t>
+  </si>
+  <si>
+    <t>PK-GEN-AZMEK-RK8KZ-RCA-1</t>
+  </si>
+  <si>
+    <t>Abu Zafar Obaidullah</t>
+  </si>
+  <si>
+    <t>PK-GEN-AZO-PYB9U-RCA-1</t>
+  </si>
+  <si>
+    <t>Sadek Khan</t>
+  </si>
+  <si>
+    <t>PK-GEN-SK-4PS4E-RCA-1</t>
+  </si>
+  <si>
+    <t>Saadia Abbasi</t>
+  </si>
+  <si>
+    <t>PK-GEN-SA-1EBJ0-RCA-1</t>
+  </si>
+  <si>
+    <t>Simeen Hussain Rimi</t>
+  </si>
+  <si>
+    <t>PK-GEN-SHR-E9JJU-RCA-1</t>
+  </si>
+  <si>
+    <t>Chaudhry</t>
+  </si>
+  <si>
+    <t>PK-GEN-C-I99JD-RCA-1</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color indexed="8"/>
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="11"/>
@@ -661,7 +1129,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -669,12 +1137,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -692,126 +1169,16 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
-  <a:themeElements>
-    <a:clrScheme name="LibreOffice">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="ffffff"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="000000"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="ffffff"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="18a303"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="0369a3"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="a33e03"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8e03a3"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="c99c00"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="c9211e"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000ee"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="551a8b"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J101"/>
-  <sheetFormatPr defaultRowHeight="12.8" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="11.53515625" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="29.12" customWidth="1"/>
-    <col min="2" max="2" width="26.48" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:J177"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <sheetData>
-    <row r="1" ht="12.8" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -839,812 +1206,1415 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="15" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="18" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="19" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="21" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="22" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="23" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="25" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="26" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="27" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="28" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="29" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="30" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="31" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="32" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="33" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="34" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="35" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="36" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="37" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="38" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="39" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="40" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="41" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="42" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="43" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="44" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="45" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="46" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="47" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="48" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="49" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="50" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="51" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="2" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="52" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="53" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="54" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="55" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="2" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="56" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="57" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="58" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="59" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="60" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="61" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="2" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="62" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="63" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="2" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="64" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="2" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="65" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="2" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="66" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="67" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="68" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="69" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="2" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="70" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="2" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="71" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="2" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="72" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="2" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="73" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="2" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="74" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="75" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="76" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="2" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="77" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="78" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="2" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="79" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="2" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="80" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="2" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="81" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="2" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="82" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="2" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="83" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="2" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="84" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="2" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="85" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="2" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="86" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="2" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="87" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="2" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="88" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="2" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="89" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="90" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="2" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="91" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="2" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="92" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="2" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="93" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="2" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="94" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="2" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="95" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="2" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="96" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="2" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="97" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="2" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="98" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="2" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="99" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="2" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="100" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="2" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="101" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="2" t="s">
         <v>202</v>
       </c>
     </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>